--- a/ASC.L.xlsx
+++ b/ASC.L.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1542E2F-B391-472E-BBED-884FD0D0E923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F795C8-45CC-4C89-AB0A-1762D0B2B51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{FCC89055-8009-4D10-BE57-380037B28F79}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{FCC89055-8009-4D10-BE57-380037B28F79}"/>
   </bookViews>
   <sheets>
     <sheet name="Main " sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t xml:space="preserve">Aosos </t>
   </si>
@@ -81,9 +81,6 @@
     <t xml:space="preserve">Conversion </t>
   </si>
   <si>
-    <t>Income Statement</t>
-  </si>
-  <si>
     <t>Revenue</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
   </si>
   <si>
     <t xml:space="preserve">Shares </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance Sheet </t>
   </si>
   <si>
     <t>Goodwill &amp; Intangibles</t>
@@ -216,10 +210,13 @@
     <t xml:space="preserve">Equity &amp; Liabilties </t>
   </si>
   <si>
-    <t>FQ424</t>
+    <t>numbers in mio GBP</t>
   </si>
   <si>
-    <t>numbers in mio GBP</t>
+    <t>GMV</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -236,6 +233,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -272,13 +275,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -299,22 +295,25 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -665,13 +664,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>4.3620000000000001</v>
+        <v>2.4350000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -679,14 +678,14 @@
         <v>3</v>
       </c>
       <c r="F3" s="3">
-        <v>119.08516</v>
+        <v>119.294826</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -694,7 +693,7 @@
       </c>
       <c r="F4" s="3">
         <f>+F2*F3</f>
-        <v>519.44946792000007</v>
+        <v>290.48290130999999</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -702,9 +701,9 @@
         <v>5</v>
       </c>
       <c r="F5" s="3">
-        <v>391</v>
+        <v>318.89999999999998</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -713,10 +712,10 @@
         <v>6</v>
       </c>
       <c r="F6" s="3">
-        <f>1.6+686.5</f>
-        <v>688.1</v>
+        <f>407.2+96.4</f>
+        <v>503.6</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="12" t="s">
         <v>59</v>
       </c>
     </row>
@@ -726,7 +725,7 @@
       </c>
       <c r="F7" s="3">
         <f>+F4-F5+F6</f>
-        <v>816.5494679200001</v>
+        <v>475.18290131000003</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -748,7 +747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C168DE0F-96D7-4A5E-B61A-8C787FBBE49C}">
-  <dimension ref="A1:DA459"/>
+  <dimension ref="A1:DA455"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -757,7 +756,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:105" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -771,57 +770,45 @@
       <c r="I2" s="2">
         <v>2024</v>
       </c>
+      <c r="J2" s="2">
+        <v>2025</v>
+      </c>
     </row>
     <row r="3" spans="1:105" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
-        <v>9</v>
+      <c r="B3" s="9" t="s">
+        <v>58</v>
       </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3">
-        <v>23.3</v>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3">
+        <v>2817.8</v>
       </c>
-      <c r="I3" s="3">
-        <v>19.600000000000001</v>
+      <c r="J3" s="3">
+        <v>2456.3000000000002</v>
       </c>
-      <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
     </row>
     <row r="4" spans="1:105" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3">
-        <v>83.7</v>
+        <v>23.3</v>
       </c>
       <c r="I4" s="3">
-        <v>67.2</v>
+        <v>19.7</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="3">
+        <v>17</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -844,19 +831,21 @@
     </row>
     <row r="5" spans="1:105" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3">
-        <v>40.33</v>
+        <v>83.7</v>
       </c>
       <c r="I5" s="3">
-        <v>41.07</v>
+        <v>67.2</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="J5" s="3">
+        <v>57.3</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -879,19 +868,21 @@
     </row>
     <row r="6" spans="1:105" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>2661.3</v>
+        <v>40.33</v>
       </c>
       <c r="I6" s="3">
-        <v>2252.4</v>
+        <v>41.07</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <v>43.36</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -914,29 +905,73 @@
     </row>
     <row r="7" spans="1:105" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>2661.3</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2252.4</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1912.9</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+    </row>
+    <row r="8" spans="1:105" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H8" s="5">
         <v>3.1E-2</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I8" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="J8" s="6">
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:105" x14ac:dyDescent="0.2">
-      <c r="B9" s="8" t="s">
+    <row r="10" spans="1:105" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:105" x14ac:dyDescent="0.2">
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8">
+        <v>3549.5</v>
+      </c>
+      <c r="I10" s="8">
+        <v>2905.8</v>
+      </c>
+      <c r="J10" s="8">
+        <v>2477.8000000000002</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1043,12 +1078,14 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3">
-        <v>3549.5</v>
+        <v>2090.5</v>
       </c>
       <c r="I11" s="3">
-        <v>2905.8</v>
+        <v>1743.3</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3">
+        <v>1311.1</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1155,12 +1192,17 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3">
-        <v>2090.5</v>
+        <f>+H10-H11</f>
+        <v>1459</v>
       </c>
       <c r="I12" s="3">
-        <v>1743.3</v>
+        <f>+I10-I11</f>
+        <v>1162.5000000000002</v>
       </c>
-      <c r="J12" s="3"/>
+      <c r="J12" s="3">
+        <f>+J10-J11</f>
+        <v>1166.7000000000003</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1267,14 +1309,14 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3">
-        <f>+H11-H12</f>
-        <v>1459</v>
+        <v>429.7</v>
       </c>
       <c r="I13" s="3">
-        <f>+I11-I12</f>
-        <v>1162.5000000000002</v>
+        <v>326.10000000000002</v>
       </c>
-      <c r="J13" s="3"/>
+      <c r="J13" s="11">
+        <v>262.3</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -1381,12 +1423,14 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3">
-        <v>429.7</v>
+        <v>1279.8</v>
       </c>
       <c r="I14" s="3">
-        <v>326.10000000000002</v>
+        <v>1170.3</v>
       </c>
-      <c r="J14" s="3"/>
+      <c r="J14" s="11">
+        <v>1133.2</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -1493,12 +1537,14 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3">
-        <v>1279.8</v>
+        <v>2</v>
       </c>
       <c r="I15" s="3">
-        <v>1170.3</v>
+        <v>2</v>
       </c>
-      <c r="J15" s="3"/>
+      <c r="J15" s="11">
+        <v>16.5</v>
+      </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -1603,14 +1649,22 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3">
+        <f t="shared" ref="G16:H16" si="0">+G12-SUM(G13:G14)+G15</f>
+        <v>0</v>
+      </c>
       <c r="H16" s="3">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>-248.5</v>
       </c>
       <c r="I16" s="3">
-        <v>2</v>
+        <f>+I12-SUM(I13:I14)+I15</f>
+        <v>-331.89999999999986</v>
       </c>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <f>+J12-SUM(J13:J14)+J15</f>
+        <v>-212.29999999999973</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -1715,19 +1769,16 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3">
-        <f t="shared" ref="G17:H17" si="0">+G13-SUM(G14:G15)+G16</f>
-        <v>0</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3">
-        <f t="shared" si="0"/>
-        <v>-248.5</v>
+        <v>5</v>
       </c>
       <c r="I17" s="3">
-        <f>+I13-SUM(I14:I15)+I16</f>
-        <v>-331.89999999999986</v>
+        <v>12</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>4.8</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -1834,12 +1885,14 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3">
-        <v>5</v>
+        <v>53.2</v>
       </c>
       <c r="I18" s="3">
-        <v>12</v>
+        <v>59.4</v>
       </c>
-      <c r="J18" s="3"/>
+      <c r="J18" s="3">
+        <v>74.099999999999994</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -1944,14 +1997,22 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3">
+        <f t="shared" ref="G19" si="1">+G16-G18+G17</f>
+        <v>0</v>
+      </c>
       <c r="H19" s="3">
-        <v>53.2</v>
+        <f>+H16-H18+H17</f>
+        <v>-296.7</v>
       </c>
       <c r="I19" s="3">
-        <v>59.4</v>
+        <f>+I16-I18+I17</f>
+        <v>-379.29999999999984</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3">
+        <f>+J16-J18+J17</f>
+        <v>-281.59999999999974</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -2056,19 +2117,16 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3">
-        <f t="shared" ref="G20" si="1">+G17-G19+G18</f>
-        <v>0</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3">
-        <f>+H17-H19+H18</f>
-        <v>-296.7</v>
+        <v>-73.599999999999994</v>
       </c>
       <c r="I20" s="3">
-        <f>+I17-I19+I18</f>
-        <v>-379.29999999999984</v>
+        <v>-40.6</v>
       </c>
-      <c r="J20" s="3"/>
+      <c r="J20" s="3">
+        <v>16.8</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -2173,14 +2231,22 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3">
+        <f>+G19-G20</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="3">
-        <v>-73.599999999999994</v>
+        <f>+H19-H20</f>
+        <v>-223.1</v>
       </c>
       <c r="I21" s="3">
-        <v>-40.6</v>
+        <f>+I19-I20</f>
+        <v>-338.69999999999982</v>
       </c>
-      <c r="J21" s="3"/>
+      <c r="J21" s="3">
+        <f>+J19-J20</f>
+        <v>-298.39999999999975</v>
+      </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -2278,25 +2344,13 @@
       <c r="DA21" s="3"/>
     </row>
     <row r="22" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="3">
-        <f>+G20-G21</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <f>+H20-H21</f>
-        <v>-223.1</v>
-      </c>
-      <c r="I22" s="3">
-        <f>+I20-I21</f>
-        <v>-338.69999999999982</v>
-      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
@@ -2395,14 +2449,24 @@
       <c r="DA22" s="3"/>
     </row>
     <row r="23" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
+      <c r="H23" s="3">
+        <v>-2.13</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-2.8439999999999999</v>
+      </c>
+      <c r="J23" s="3">
+        <f>+J21/J24</f>
+        <v>-2.5013658178268332</v>
+      </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -2508,13 +2572,13 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3">
-        <v>-2.13</v>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3">
+        <v>119.08526000000001</v>
       </c>
-      <c r="I24" s="3">
-        <v>-2.8439999999999999</v>
+      <c r="J24" s="3">
+        <v>119.294826</v>
       </c>
-      <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -2612,9 +2676,6 @@
       <c r="DA24" s="3"/>
     </row>
     <row r="25" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -2825,14 +2886,26 @@
       <c r="DA26" s="3"/>
     </row>
     <row r="27" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="B27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="10" t="e">
+        <f>+H10/G10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I27" s="10">
+        <f>+I10/H10-1</f>
+        <v>-0.18134948584307642</v>
+      </c>
+      <c r="J27" s="10">
+        <f>+J10/I10-1</f>
+        <v>-0.14729162364925319</v>
+      </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -2931,22 +3004,25 @@
     </row>
     <row r="28" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="9" t="e">
-        <f>+H11/G11-1</f>
-        <v>#DIV/0!</v>
+      <c r="H28" s="7">
+        <f>+H12/H10</f>
+        <v>0.41104380898718129</v>
       </c>
-      <c r="I28" s="9">
-        <f>+I11/H11-1</f>
-        <v>-0.18134948584307642</v>
+      <c r="I28" s="7">
+        <f>+I12/I10</f>
+        <v>0.40006194507536658</v>
       </c>
-      <c r="J28" s="3"/>
+      <c r="J28" s="7">
+        <f>+J12/J10</f>
+        <v>0.470861247881185</v>
+      </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -3045,22 +3121,25 @@
     </row>
     <row r="29" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="9">
-        <f>+H13/H11</f>
-        <v>0.41104380898718129</v>
+      <c r="H29" s="7">
+        <f>+H16/H10</f>
+        <v>-7.0009860543738561E-2</v>
       </c>
-      <c r="I29" s="9">
-        <f>+I13/I11</f>
-        <v>0.40006194507536658</v>
+      <c r="I29" s="7">
+        <f>+I16/I10</f>
+        <v>-0.11421983618968953</v>
       </c>
-      <c r="J29" s="3"/>
+      <c r="J29" s="7">
+        <f>+J16/J10</f>
+        <v>-8.5680845911695738E-2</v>
+      </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -3158,22 +3237,13 @@
       <c r="DA29" s="3"/>
     </row>
     <row r="30" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="9">
-        <f>+H17/H11</f>
-        <v>-7.0009860543738561E-2</v>
-      </c>
-      <c r="I30" s="9">
-        <f>+I17/I11</f>
-        <v>-0.11421983618968953</v>
-      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
@@ -3377,14 +3447,23 @@
       <c r="DA31" s="3"/>
     </row>
     <row r="32" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="H32" s="3">
+        <v>700.5</v>
+      </c>
+      <c r="I32" s="3">
+        <v>514</v>
+      </c>
+      <c r="J32" s="3">
+        <v>473.6</v>
+      </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -3482,14 +3561,23 @@
       <c r="DA32" s="3"/>
     </row>
     <row r="33" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="H33" s="3">
+        <v>362.6</v>
+      </c>
+      <c r="I33" s="3">
+        <v>283.2</v>
+      </c>
+      <c r="J33" s="3">
+        <v>153.4</v>
+      </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -3587,17 +3675,23 @@
       <c r="DA33" s="3"/>
     </row>
     <row r="34" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B34" s="8" t="s">
-        <v>29</v>
+      <c r="B34" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
+      <c r="H34" s="3">
+        <v>295.2</v>
+      </c>
+      <c r="I34" s="3">
+        <v>254</v>
+      </c>
+      <c r="J34" s="3">
+        <v>172.1</v>
+      </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -3695,14 +3789,23 @@
       <c r="DA34" s="3"/>
     </row>
     <row r="35" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="H35" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="I35" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="J35" s="3">
+        <v>6.2</v>
+      </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -3801,7 +3904,7 @@
     </row>
     <row r="36" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -3809,12 +3912,14 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3">
-        <v>700.5</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>514</v>
+        <v>3.7</v>
       </c>
-      <c r="J36" s="3"/>
+      <c r="J36" s="3">
+        <v>44.9</v>
+      </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -3913,7 +4018,7 @@
     </row>
     <row r="37" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -3921,12 +4026,15 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3">
-        <v>362.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I37" s="3">
-        <v>283.2</v>
+        <v>0.3</v>
       </c>
-      <c r="J37" s="3"/>
+      <c r="J37" s="3">
+        <f>1.8+0.1</f>
+        <v>1.9000000000000001</v>
+      </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -4025,7 +4133,7 @@
     </row>
     <row r="38" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -4033,12 +4141,14 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3">
-        <v>295.2</v>
+        <v>17.8</v>
       </c>
       <c r="I38" s="3">
-        <v>254</v>
+        <v>62.5</v>
       </c>
-      <c r="J38" s="3"/>
+      <c r="J38" s="3">
+        <v>44.7</v>
+      </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -4137,20 +4247,28 @@
     </row>
     <row r="39" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="G39" s="3">
+        <f t="shared" ref="G39:H39" si="2">+SUM(G32:G38)</f>
+        <v>0</v>
+      </c>
       <c r="H39" s="3">
-        <v>10.9</v>
+        <f t="shared" si="2"/>
+        <v>1391.1</v>
       </c>
       <c r="I39" s="3">
-        <v>7.1</v>
+        <f>+SUM(I32:I38)</f>
+        <v>1124.8</v>
       </c>
-      <c r="J39" s="3"/>
+      <c r="J39" s="3">
+        <f>+SUM(J32:J38)</f>
+        <v>896.80000000000007</v>
+      </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -4249,7 +4367,7 @@
     </row>
     <row r="40" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -4257,12 +4375,14 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="I40" s="3">
-        <v>3.7</v>
+        <v>520.29999999999995</v>
       </c>
-      <c r="J40" s="3"/>
+      <c r="J40" s="3">
+        <v>402.3</v>
+      </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
@@ -4361,7 +4481,7 @@
     </row>
     <row r="41" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -4369,12 +4489,14 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3">
-        <v>4.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>0.3</v>
+        <v>165.5</v>
       </c>
-      <c r="J41" s="3"/>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4473,7 +4595,7 @@
     </row>
     <row r="42" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -4481,12 +4603,14 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3">
-        <v>17.8</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="I42" s="3">
-        <v>62.5</v>
+        <v>53.4</v>
       </c>
-      <c r="J42" s="3"/>
+      <c r="J42" s="3">
+        <v>49.2</v>
+      </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -4585,25 +4709,22 @@
     </row>
     <row r="43" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="3">
-        <f t="shared" ref="G43:H43" si="2">+SUM(G36:G42)</f>
-        <v>0</v>
-      </c>
+      <c r="G43" s="3"/>
       <c r="H43" s="3">
-        <f t="shared" si="2"/>
-        <v>1391.1</v>
+        <v>22.4</v>
       </c>
       <c r="I43" s="3">
-        <f>+SUM(I36:I42)</f>
-        <v>1124.8</v>
+        <v>9.5</v>
       </c>
-      <c r="J43" s="3"/>
+      <c r="J43" s="3">
+        <v>1.2</v>
+      </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
@@ -4702,7 +4823,7 @@
     </row>
     <row r="44" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -4710,12 +4831,14 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3">
-        <v>780</v>
+        <v>353.3</v>
       </c>
       <c r="I44" s="3">
-        <v>520.29999999999995</v>
+        <v>391</v>
       </c>
-      <c r="J44" s="3"/>
+      <c r="J44" s="3">
+        <v>318.89999999999998</v>
+      </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4822,12 +4945,14 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I45" s="3">
-        <v>165.5</v>
+        <v>6.7</v>
       </c>
-      <c r="J45" s="3"/>
+      <c r="J45" s="3">
+        <v>3.7</v>
+      </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
@@ -4932,14 +5057,22 @@
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="G46" s="3">
+        <f t="shared" ref="G46:H46" si="3">+SUM(G40:G45)</f>
+        <v>0</v>
+      </c>
       <c r="H46" s="3">
-        <v>81.400000000000006</v>
+        <f t="shared" si="3"/>
+        <v>1246.5</v>
       </c>
       <c r="I46" s="3">
-        <v>53.4</v>
+        <f>+SUM(I40:I45)</f>
+        <v>1146.3999999999999</v>
       </c>
-      <c r="J46" s="3"/>
+      <c r="J46" s="3">
+        <f>+SUM(J40:J45)</f>
+        <v>775.3</v>
+      </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
@@ -5037,20 +5170,13 @@
       <c r="DA46" s="3"/>
     </row>
     <row r="47" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B47" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3">
-        <v>22.4</v>
-      </c>
-      <c r="I47" s="3">
-        <v>9.5</v>
-      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
@@ -5150,20 +5276,28 @@
     </row>
     <row r="48" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="G48" s="3">
+        <f t="shared" ref="G48:H48" si="4">+G46+G39</f>
+        <v>0</v>
+      </c>
       <c r="H48" s="3">
-        <v>353.3</v>
+        <f t="shared" si="4"/>
+        <v>2637.6</v>
       </c>
       <c r="I48" s="3">
-        <v>391</v>
+        <f>+I46+I39</f>
+        <v>2271.1999999999998</v>
       </c>
-      <c r="J48" s="3"/>
+      <c r="J48" s="3">
+        <f>+J46+J39</f>
+        <v>1672.1</v>
+      </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
@@ -5261,20 +5395,13 @@
       <c r="DA48" s="3"/>
     </row>
     <row r="49" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B49" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="3">
-        <v>9.4</v>
-      </c>
-      <c r="I49" s="3">
-        <v>6.7</v>
-      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -5374,25 +5501,22 @@
     </row>
     <row r="50" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-      <c r="G50" s="3">
-        <f t="shared" ref="G50:H50" si="3">+SUM(G44:G49)</f>
-        <v>0</v>
-      </c>
+      <c r="G50" s="3"/>
       <c r="H50" s="3">
-        <f t="shared" si="3"/>
-        <v>1246.5</v>
+        <v>680.4</v>
       </c>
       <c r="I50" s="3">
-        <f>+SUM(I44:I49)</f>
-        <v>1146.3999999999999</v>
+        <v>671.7</v>
       </c>
-      <c r="J50" s="3"/>
+      <c r="J50" s="3">
+        <v>619.29999999999995</v>
+      </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
@@ -5490,14 +5614,23 @@
       <c r="DA50" s="3"/>
     </row>
     <row r="51" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="B51" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
+      <c r="H51" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="I51" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="J51" s="3">
+        <v>96.4</v>
+      </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -5596,25 +5729,22 @@
     </row>
     <row r="52" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
-      <c r="G52" s="3">
-        <f t="shared" ref="G52:H52" si="4">+G50+G43</f>
-        <v>0</v>
-      </c>
+      <c r="G52" s="3"/>
       <c r="H52" s="3">
-        <f t="shared" si="4"/>
-        <v>2637.6</v>
+        <v>25.3</v>
       </c>
       <c r="I52" s="3">
-        <f>+I50+I43</f>
-        <v>2271.1999999999998</v>
+        <v>27.2</v>
       </c>
-      <c r="J52" s="3"/>
+      <c r="J52" s="3">
+        <v>27.5</v>
+      </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
@@ -5712,14 +5842,23 @@
       <c r="DA52" s="3"/>
     </row>
     <row r="53" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="B53" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
+      <c r="H53" s="3">
+        <v>6</v>
+      </c>
+      <c r="I53" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="J53" s="3">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -5818,7 +5957,7 @@
     </row>
     <row r="54" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
@@ -5826,12 +5965,14 @@
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3">
-        <v>680.4</v>
+        <v>2</v>
       </c>
       <c r="I54" s="3">
-        <v>671.7</v>
+        <v>2.7</v>
       </c>
-      <c r="J54" s="3"/>
+      <c r="J54" s="3">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -5930,7 +6071,7 @@
     </row>
     <row r="55" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -5938,12 +6079,14 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I55" s="3">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
-      <c r="J55" s="3"/>
+      <c r="J55" s="3">
+        <v>0</v>
+      </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -6042,20 +6185,28 @@
     </row>
     <row r="56" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="G56" s="3">
+        <f t="shared" ref="G56:H56" si="5">+SUM(G50:G55)</f>
+        <v>0</v>
+      </c>
       <c r="H56" s="3">
-        <v>25.3</v>
+        <f t="shared" si="5"/>
+        <v>715.19999999999993</v>
       </c>
       <c r="I56" s="3">
-        <v>27.2</v>
+        <f>+SUM(I50:I55)</f>
+        <v>714.00000000000023</v>
       </c>
-      <c r="J56" s="3"/>
+      <c r="J56" s="3">
+        <f>+SUM(J50:J55)</f>
+        <v>757.39999999999986</v>
+      </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -6154,7 +6305,7 @@
     </row>
     <row r="57" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -6162,12 +6313,14 @@
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3">
-        <v>6</v>
+        <v>671.3</v>
       </c>
       <c r="I57" s="3">
-        <v>6.6</v>
+        <v>686.5</v>
       </c>
-      <c r="J57" s="3"/>
+      <c r="J57" s="3">
+        <v>407.2</v>
+      </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
@@ -6266,7 +6419,7 @@
     </row>
     <row r="58" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
@@ -6274,12 +6427,14 @@
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3">
-        <v>2</v>
+        <v>303.7</v>
       </c>
       <c r="I58" s="3">
-        <v>2.7</v>
+        <v>262.39999999999998</v>
       </c>
-      <c r="J58" s="3"/>
+      <c r="J58" s="3">
+        <v>197</v>
+      </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
@@ -6378,7 +6533,7 @@
     </row>
     <row r="59" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -6386,12 +6541,14 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I59" s="3">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
-      <c r="J59" s="3"/>
+      <c r="J59" s="3">
+        <v>0.3</v>
+      </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
@@ -6490,25 +6647,22 @@
     </row>
     <row r="60" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-      <c r="G60" s="3">
-        <f t="shared" ref="G60:H60" si="5">+SUM(G54:G59)</f>
-        <v>0</v>
-      </c>
+      <c r="G60" s="3"/>
       <c r="H60" s="3">
-        <f t="shared" si="5"/>
-        <v>715.19999999999993</v>
+        <v>68.2</v>
       </c>
       <c r="I60" s="3">
-        <f>+SUM(I54:I59)</f>
-        <v>714.00000000000023</v>
+        <v>86.5</v>
       </c>
-      <c r="J60" s="3"/>
+      <c r="J60" s="3">
+        <v>97.8</v>
+      </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
@@ -6607,20 +6761,28 @@
     </row>
     <row r="61" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+      <c r="G61" s="3">
+        <f t="shared" ref="G61:H61" si="6">+SUM(G57:G60)</f>
+        <v>0</v>
+      </c>
       <c r="H61" s="3">
-        <v>671.3</v>
+        <f t="shared" si="6"/>
+        <v>1043.7</v>
       </c>
       <c r="I61" s="3">
-        <v>686.5</v>
+        <f>+SUM(I57:I60)</f>
+        <v>1035.9000000000001</v>
       </c>
-      <c r="J61" s="3"/>
+      <c r="J61" s="3">
+        <f>+SUM(J57:J60)</f>
+        <v>702.3</v>
+      </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
@@ -6718,20 +6880,13 @@
       <c r="DA61" s="3"/>
     </row>
     <row r="62" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B62" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="3">
-        <v>303.7</v>
-      </c>
-      <c r="I62" s="3">
-        <v>262.39999999999998</v>
-      </c>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
@@ -6831,7 +6986,7 @@
     </row>
     <row r="63" spans="2:105" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
@@ -6839,12 +6994,14 @@
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3">
-        <v>0.5</v>
+        <v>866.7</v>
       </c>
       <c r="I63" s="3">
-        <v>0.5</v>
+        <v>521.29999999999995</v>
       </c>
-      <c r="J63" s="3"/>
+      <c r="J63" s="3">
+        <v>212.4</v>
+      </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
@@ -6942,20 +7099,13 @@
       <c r="DA63" s="3"/>
     </row>
     <row r="64" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B64" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="3">
-        <v>68.2</v>
-      </c>
-      <c r="I64" s="3">
-        <v>86.5</v>
-      </c>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
@@ -7062,18 +7212,21 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3">
-        <f t="shared" ref="G65:H65" si="6">+SUM(G61:G64)</f>
+        <f t="shared" ref="G65:H65" si="7">+G63+G61+G56</f>
         <v>0</v>
       </c>
       <c r="H65" s="3">
-        <f t="shared" si="6"/>
-        <v>1043.7</v>
+        <f t="shared" si="7"/>
+        <v>2625.6</v>
       </c>
       <c r="I65" s="3">
-        <f>+SUM(I61:I64)</f>
-        <v>1035.9000000000001</v>
+        <f>+I63+I61+I56</f>
+        <v>2271.2000000000003</v>
       </c>
-      <c r="J65" s="3"/>
+      <c r="J65" s="3">
+        <f>+J63+J61+J56</f>
+        <v>1672.1</v>
+      </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
@@ -7276,20 +7429,13 @@
       <c r="DA66" s="3"/>
     </row>
     <row r="67" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B67" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="3">
-        <v>866.7</v>
-      </c>
-      <c r="I67" s="3">
-        <v>521.29999999999995</v>
-      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
@@ -7493,25 +7639,13 @@
       <c r="DA68" s="3"/>
     </row>
     <row r="69" spans="2:105" x14ac:dyDescent="0.2">
-      <c r="B69" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="3">
-        <f t="shared" ref="G69:H69" si="7">+G67+G65+G60</f>
-        <v>0</v>
-      </c>
-      <c r="H69" s="3">
-        <f t="shared" si="7"/>
-        <v>2625.6</v>
-      </c>
-      <c r="I69" s="3">
-        <f>+I67+I65+I60</f>
-        <v>2271.2000000000003</v>
-      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
@@ -48139,426 +48273,6 @@
       <c r="CZ455" s="3"/>
       <c r="DA455" s="3"/>
     </row>
-    <row r="456" spans="3:105" x14ac:dyDescent="0.2">
-      <c r="C456" s="3"/>
-      <c r="D456" s="3"/>
-      <c r="E456" s="3"/>
-      <c r="F456" s="3"/>
-      <c r="G456" s="3"/>
-      <c r="H456" s="3"/>
-      <c r="I456" s="3"/>
-      <c r="J456" s="3"/>
-      <c r="K456" s="3"/>
-      <c r="L456" s="3"/>
-      <c r="M456" s="3"/>
-      <c r="N456" s="3"/>
-      <c r="O456" s="3"/>
-      <c r="P456" s="3"/>
-      <c r="Q456" s="3"/>
-      <c r="R456" s="3"/>
-      <c r="S456" s="3"/>
-      <c r="T456" s="3"/>
-      <c r="U456" s="3"/>
-      <c r="V456" s="3"/>
-      <c r="W456" s="3"/>
-      <c r="X456" s="3"/>
-      <c r="Y456" s="3"/>
-      <c r="Z456" s="3"/>
-      <c r="AA456" s="3"/>
-      <c r="AB456" s="3"/>
-      <c r="AC456" s="3"/>
-      <c r="AD456" s="3"/>
-      <c r="AE456" s="3"/>
-      <c r="AF456" s="3"/>
-      <c r="AG456" s="3"/>
-      <c r="AH456" s="3"/>
-      <c r="AI456" s="3"/>
-      <c r="AJ456" s="3"/>
-      <c r="AK456" s="3"/>
-      <c r="AL456" s="3"/>
-      <c r="AM456" s="3"/>
-      <c r="AN456" s="3"/>
-      <c r="AO456" s="3"/>
-      <c r="AP456" s="3"/>
-      <c r="AQ456" s="3"/>
-      <c r="AR456" s="3"/>
-      <c r="AS456" s="3"/>
-      <c r="AT456" s="3"/>
-      <c r="AU456" s="3"/>
-      <c r="AV456" s="3"/>
-      <c r="AW456" s="3"/>
-      <c r="AX456" s="3"/>
-      <c r="AY456" s="3"/>
-      <c r="AZ456" s="3"/>
-      <c r="BA456" s="3"/>
-      <c r="BB456" s="3"/>
-      <c r="BC456" s="3"/>
-      <c r="BD456" s="3"/>
-      <c r="BE456" s="3"/>
-      <c r="BF456" s="3"/>
-      <c r="BG456" s="3"/>
-      <c r="BH456" s="3"/>
-      <c r="BI456" s="3"/>
-      <c r="BJ456" s="3"/>
-      <c r="BK456" s="3"/>
-      <c r="BL456" s="3"/>
-      <c r="BM456" s="3"/>
-      <c r="BN456" s="3"/>
-      <c r="BO456" s="3"/>
-      <c r="BP456" s="3"/>
-      <c r="BQ456" s="3"/>
-      <c r="BR456" s="3"/>
-      <c r="BS456" s="3"/>
-      <c r="BT456" s="3"/>
-      <c r="BU456" s="3"/>
-      <c r="BV456" s="3"/>
-      <c r="BW456" s="3"/>
-      <c r="BX456" s="3"/>
-      <c r="BY456" s="3"/>
-      <c r="BZ456" s="3"/>
-      <c r="CA456" s="3"/>
-      <c r="CB456" s="3"/>
-      <c r="CC456" s="3"/>
-      <c r="CD456" s="3"/>
-      <c r="CE456" s="3"/>
-      <c r="CF456" s="3"/>
-      <c r="CG456" s="3"/>
-      <c r="CH456" s="3"/>
-      <c r="CI456" s="3"/>
-      <c r="CJ456" s="3"/>
-      <c r="CK456" s="3"/>
-      <c r="CL456" s="3"/>
-      <c r="CM456" s="3"/>
-      <c r="CN456" s="3"/>
-      <c r="CO456" s="3"/>
-      <c r="CP456" s="3"/>
-      <c r="CQ456" s="3"/>
-      <c r="CR456" s="3"/>
-      <c r="CS456" s="3"/>
-      <c r="CT456" s="3"/>
-      <c r="CU456" s="3"/>
-      <c r="CV456" s="3"/>
-      <c r="CW456" s="3"/>
-      <c r="CX456" s="3"/>
-      <c r="CY456" s="3"/>
-      <c r="CZ456" s="3"/>
-      <c r="DA456" s="3"/>
-    </row>
-    <row r="457" spans="3:105" x14ac:dyDescent="0.2">
-      <c r="C457" s="3"/>
-      <c r="D457" s="3"/>
-      <c r="E457" s="3"/>
-      <c r="F457" s="3"/>
-      <c r="G457" s="3"/>
-      <c r="H457" s="3"/>
-      <c r="I457" s="3"/>
-      <c r="J457" s="3"/>
-      <c r="K457" s="3"/>
-      <c r="L457" s="3"/>
-      <c r="M457" s="3"/>
-      <c r="N457" s="3"/>
-      <c r="O457" s="3"/>
-      <c r="P457" s="3"/>
-      <c r="Q457" s="3"/>
-      <c r="R457" s="3"/>
-      <c r="S457" s="3"/>
-      <c r="T457" s="3"/>
-      <c r="U457" s="3"/>
-      <c r="V457" s="3"/>
-      <c r="W457" s="3"/>
-      <c r="X457" s="3"/>
-      <c r="Y457" s="3"/>
-      <c r="Z457" s="3"/>
-      <c r="AA457" s="3"/>
-      <c r="AB457" s="3"/>
-      <c r="AC457" s="3"/>
-      <c r="AD457" s="3"/>
-      <c r="AE457" s="3"/>
-      <c r="AF457" s="3"/>
-      <c r="AG457" s="3"/>
-      <c r="AH457" s="3"/>
-      <c r="AI457" s="3"/>
-      <c r="AJ457" s="3"/>
-      <c r="AK457" s="3"/>
-      <c r="AL457" s="3"/>
-      <c r="AM457" s="3"/>
-      <c r="AN457" s="3"/>
-      <c r="AO457" s="3"/>
-      <c r="AP457" s="3"/>
-      <c r="AQ457" s="3"/>
-      <c r="AR457" s="3"/>
-      <c r="AS457" s="3"/>
-      <c r="AT457" s="3"/>
-      <c r="AU457" s="3"/>
-      <c r="AV457" s="3"/>
-      <c r="AW457" s="3"/>
-      <c r="AX457" s="3"/>
-      <c r="AY457" s="3"/>
-      <c r="AZ457" s="3"/>
-      <c r="BA457" s="3"/>
-      <c r="BB457" s="3"/>
-      <c r="BC457" s="3"/>
-      <c r="BD457" s="3"/>
-      <c r="BE457" s="3"/>
-      <c r="BF457" s="3"/>
-      <c r="BG457" s="3"/>
-      <c r="BH457" s="3"/>
-      <c r="BI457" s="3"/>
-      <c r="BJ457" s="3"/>
-      <c r="BK457" s="3"/>
-      <c r="BL457" s="3"/>
-      <c r="BM457" s="3"/>
-      <c r="BN457" s="3"/>
-      <c r="BO457" s="3"/>
-      <c r="BP457" s="3"/>
-      <c r="BQ457" s="3"/>
-      <c r="BR457" s="3"/>
-      <c r="BS457" s="3"/>
-      <c r="BT457" s="3"/>
-      <c r="BU457" s="3"/>
-      <c r="BV457" s="3"/>
-      <c r="BW457" s="3"/>
-      <c r="BX457" s="3"/>
-      <c r="BY457" s="3"/>
-      <c r="BZ457" s="3"/>
-      <c r="CA457" s="3"/>
-      <c r="CB457" s="3"/>
-      <c r="CC457" s="3"/>
-      <c r="CD457" s="3"/>
-      <c r="CE457" s="3"/>
-      <c r="CF457" s="3"/>
-      <c r="CG457" s="3"/>
-      <c r="CH457" s="3"/>
-      <c r="CI457" s="3"/>
-      <c r="CJ457" s="3"/>
-      <c r="CK457" s="3"/>
-      <c r="CL457" s="3"/>
-      <c r="CM457" s="3"/>
-      <c r="CN457" s="3"/>
-      <c r="CO457" s="3"/>
-      <c r="CP457" s="3"/>
-      <c r="CQ457" s="3"/>
-      <c r="CR457" s="3"/>
-      <c r="CS457" s="3"/>
-      <c r="CT457" s="3"/>
-      <c r="CU457" s="3"/>
-      <c r="CV457" s="3"/>
-      <c r="CW457" s="3"/>
-      <c r="CX457" s="3"/>
-      <c r="CY457" s="3"/>
-      <c r="CZ457" s="3"/>
-      <c r="DA457" s="3"/>
-    </row>
-    <row r="458" spans="3:105" x14ac:dyDescent="0.2">
-      <c r="C458" s="3"/>
-      <c r="D458" s="3"/>
-      <c r="E458" s="3"/>
-      <c r="F458" s="3"/>
-      <c r="G458" s="3"/>
-      <c r="H458" s="3"/>
-      <c r="I458" s="3"/>
-      <c r="J458" s="3"/>
-      <c r="K458" s="3"/>
-      <c r="L458" s="3"/>
-      <c r="M458" s="3"/>
-      <c r="N458" s="3"/>
-      <c r="O458" s="3"/>
-      <c r="P458" s="3"/>
-      <c r="Q458" s="3"/>
-      <c r="R458" s="3"/>
-      <c r="S458" s="3"/>
-      <c r="T458" s="3"/>
-      <c r="U458" s="3"/>
-      <c r="V458" s="3"/>
-      <c r="W458" s="3"/>
-      <c r="X458" s="3"/>
-      <c r="Y458" s="3"/>
-      <c r="Z458" s="3"/>
-      <c r="AA458" s="3"/>
-      <c r="AB458" s="3"/>
-      <c r="AC458" s="3"/>
-      <c r="AD458" s="3"/>
-      <c r="AE458" s="3"/>
-      <c r="AF458" s="3"/>
-      <c r="AG458" s="3"/>
-      <c r="AH458" s="3"/>
-      <c r="AI458" s="3"/>
-      <c r="AJ458" s="3"/>
-      <c r="AK458" s="3"/>
-      <c r="AL458" s="3"/>
-      <c r="AM458" s="3"/>
-      <c r="AN458" s="3"/>
-      <c r="AO458" s="3"/>
-      <c r="AP458" s="3"/>
-      <c r="AQ458" s="3"/>
-      <c r="AR458" s="3"/>
-      <c r="AS458" s="3"/>
-      <c r="AT458" s="3"/>
-      <c r="AU458" s="3"/>
-      <c r="AV458" s="3"/>
-      <c r="AW458" s="3"/>
-      <c r="AX458" s="3"/>
-      <c r="AY458" s="3"/>
-      <c r="AZ458" s="3"/>
-      <c r="BA458" s="3"/>
-      <c r="BB458" s="3"/>
-      <c r="BC458" s="3"/>
-      <c r="BD458" s="3"/>
-      <c r="BE458" s="3"/>
-      <c r="BF458" s="3"/>
-      <c r="BG458" s="3"/>
-      <c r="BH458" s="3"/>
-      <c r="BI458" s="3"/>
-      <c r="BJ458" s="3"/>
-      <c r="BK458" s="3"/>
-      <c r="BL458" s="3"/>
-      <c r="BM458" s="3"/>
-      <c r="BN458" s="3"/>
-      <c r="BO458" s="3"/>
-      <c r="BP458" s="3"/>
-      <c r="BQ458" s="3"/>
-      <c r="BR458" s="3"/>
-      <c r="BS458" s="3"/>
-      <c r="BT458" s="3"/>
-      <c r="BU458" s="3"/>
-      <c r="BV458" s="3"/>
-      <c r="BW458" s="3"/>
-      <c r="BX458" s="3"/>
-      <c r="BY458" s="3"/>
-      <c r="BZ458" s="3"/>
-      <c r="CA458" s="3"/>
-      <c r="CB458" s="3"/>
-      <c r="CC458" s="3"/>
-      <c r="CD458" s="3"/>
-      <c r="CE458" s="3"/>
-      <c r="CF458" s="3"/>
-      <c r="CG458" s="3"/>
-      <c r="CH458" s="3"/>
-      <c r="CI458" s="3"/>
-      <c r="CJ458" s="3"/>
-      <c r="CK458" s="3"/>
-      <c r="CL458" s="3"/>
-      <c r="CM458" s="3"/>
-      <c r="CN458" s="3"/>
-      <c r="CO458" s="3"/>
-      <c r="CP458" s="3"/>
-      <c r="CQ458" s="3"/>
-      <c r="CR458" s="3"/>
-      <c r="CS458" s="3"/>
-      <c r="CT458" s="3"/>
-      <c r="CU458" s="3"/>
-      <c r="CV458" s="3"/>
-      <c r="CW458" s="3"/>
-      <c r="CX458" s="3"/>
-      <c r="CY458" s="3"/>
-      <c r="CZ458" s="3"/>
-      <c r="DA458" s="3"/>
-    </row>
-    <row r="459" spans="3:105" x14ac:dyDescent="0.2">
-      <c r="C459" s="3"/>
-      <c r="D459" s="3"/>
-      <c r="E459" s="3"/>
-      <c r="F459" s="3"/>
-      <c r="G459" s="3"/>
-      <c r="H459" s="3"/>
-      <c r="I459" s="3"/>
-      <c r="J459" s="3"/>
-      <c r="K459" s="3"/>
-      <c r="L459" s="3"/>
-      <c r="M459" s="3"/>
-      <c r="N459" s="3"/>
-      <c r="O459" s="3"/>
-      <c r="P459" s="3"/>
-      <c r="Q459" s="3"/>
-      <c r="R459" s="3"/>
-      <c r="S459" s="3"/>
-      <c r="T459" s="3"/>
-      <c r="U459" s="3"/>
-      <c r="V459" s="3"/>
-      <c r="W459" s="3"/>
-      <c r="X459" s="3"/>
-      <c r="Y459" s="3"/>
-      <c r="Z459" s="3"/>
-      <c r="AA459" s="3"/>
-      <c r="AB459" s="3"/>
-      <c r="AC459" s="3"/>
-      <c r="AD459" s="3"/>
-      <c r="AE459" s="3"/>
-      <c r="AF459" s="3"/>
-      <c r="AG459" s="3"/>
-      <c r="AH459" s="3"/>
-      <c r="AI459" s="3"/>
-      <c r="AJ459" s="3"/>
-      <c r="AK459" s="3"/>
-      <c r="AL459" s="3"/>
-      <c r="AM459" s="3"/>
-      <c r="AN459" s="3"/>
-      <c r="AO459" s="3"/>
-      <c r="AP459" s="3"/>
-      <c r="AQ459" s="3"/>
-      <c r="AR459" s="3"/>
-      <c r="AS459" s="3"/>
-      <c r="AT459" s="3"/>
-      <c r="AU459" s="3"/>
-      <c r="AV459" s="3"/>
-      <c r="AW459" s="3"/>
-      <c r="AX459" s="3"/>
-      <c r="AY459" s="3"/>
-      <c r="AZ459" s="3"/>
-      <c r="BA459" s="3"/>
-      <c r="BB459" s="3"/>
-      <c r="BC459" s="3"/>
-      <c r="BD459" s="3"/>
-      <c r="BE459" s="3"/>
-      <c r="BF459" s="3"/>
-      <c r="BG459" s="3"/>
-      <c r="BH459" s="3"/>
-      <c r="BI459" s="3"/>
-      <c r="BJ459" s="3"/>
-      <c r="BK459" s="3"/>
-      <c r="BL459" s="3"/>
-      <c r="BM459" s="3"/>
-      <c r="BN459" s="3"/>
-      <c r="BO459" s="3"/>
-      <c r="BP459" s="3"/>
-      <c r="BQ459" s="3"/>
-      <c r="BR459" s="3"/>
-      <c r="BS459" s="3"/>
-      <c r="BT459" s="3"/>
-      <c r="BU459" s="3"/>
-      <c r="BV459" s="3"/>
-      <c r="BW459" s="3"/>
-      <c r="BX459" s="3"/>
-      <c r="BY459" s="3"/>
-      <c r="BZ459" s="3"/>
-      <c r="CA459" s="3"/>
-      <c r="CB459" s="3"/>
-      <c r="CC459" s="3"/>
-      <c r="CD459" s="3"/>
-      <c r="CE459" s="3"/>
-      <c r="CF459" s="3"/>
-      <c r="CG459" s="3"/>
-      <c r="CH459" s="3"/>
-      <c r="CI459" s="3"/>
-      <c r="CJ459" s="3"/>
-      <c r="CK459" s="3"/>
-      <c r="CL459" s="3"/>
-      <c r="CM459" s="3"/>
-      <c r="CN459" s="3"/>
-      <c r="CO459" s="3"/>
-      <c r="CP459" s="3"/>
-      <c r="CQ459" s="3"/>
-      <c r="CR459" s="3"/>
-      <c r="CS459" s="3"/>
-      <c r="CT459" s="3"/>
-      <c r="CU459" s="3"/>
-      <c r="CV459" s="3"/>
-      <c r="CW459" s="3"/>
-      <c r="CX459" s="3"/>
-      <c r="CY459" s="3"/>
-      <c r="CZ459" s="3"/>
-      <c r="DA459" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'Main '!A1" display="Main " xr:uid="{A0F34EE7-3CE5-4299-A68D-7CD124C72EA2}"/>
